--- a/data/trans_camb/PCS12_SP_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 10,89</t>
+          <t>-2,33; 11,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 10,75</t>
+          <t>-2,87; 10,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,64</t>
+          <t>-1,2; 11,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 18,67</t>
+          <t>3,3; 19,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,55</t>
+          <t>3,74; 18,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 16,92</t>
+          <t>3,33; 16,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,67</t>
+          <t>2,16; 12,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 13,03</t>
+          <t>2,19; 12,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 11,99</t>
+          <t>2,59; 12,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 81,62</t>
+          <t>-11,36; 88,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 77,92</t>
+          <t>-15,21; 78,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 86,75</t>
+          <t>-6,32; 93,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 92,04</t>
+          <t>11,72; 99,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 91,69</t>
+          <t>12,76; 96,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 89,56</t>
+          <t>10,72; 85,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 71,78</t>
+          <t>8,54; 70,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 76,03</t>
+          <t>9,22; 71,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 66,65</t>
+          <t>10,86; 68,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,56</t>
+          <t>-5,05; 4,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,21</t>
+          <t>-6,95; 2,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 12,18</t>
+          <t>0,92; 11,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 3,3</t>
+          <t>-8,15; 3,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -2,51</t>
+          <t>-13,84; -2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 4,56</t>
+          <t>-5,43; 5,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 2,16</t>
+          <t>-5,27; 2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; -1,81</t>
+          <t>-9,24; -1,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,0</t>
+          <t>-1,17; 6,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 32,46</t>
+          <t>-28,45; 31,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 16,77</t>
+          <t>-37,22; 16,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 85,75</t>
+          <t>3,76; 83,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 12,15</t>
+          <t>-24,32; 12,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,1; -8,35</t>
+          <t>-41,1; -10,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 16,0</t>
+          <t>-16,25; 17,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 9,96</t>
+          <t>-20,52; 11,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,81; -8,6</t>
+          <t>-36,98; -7,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 33,07</t>
+          <t>-4,12; 32,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,94</t>
+          <t>-2,75; 9,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,89</t>
+          <t>-4,36; 6,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 18,13</t>
+          <t>6,82; 18,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 4,33</t>
+          <t>-9,39; 4,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -2,24</t>
+          <t>-15,2; -2,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 9,09</t>
+          <t>-3,84; 9,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 4,44</t>
+          <t>-4,33; 4,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; -0,16</t>
+          <t>-8,66; -0,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 11,9</t>
+          <t>2,86; 11,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 81,27</t>
+          <t>-17,44; 83,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 56,99</t>
+          <t>-27,95; 68,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,85; 172,36</t>
+          <t>39,31; 181,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 17,38</t>
+          <t>-30,02; 17,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,7; -9,06</t>
+          <t>-47,9; -9,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 37,18</t>
+          <t>-12,12; 37,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 23,99</t>
+          <t>-18,56; 24,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,14; -0,54</t>
+          <t>-37,06; 0,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,77; 62,83</t>
+          <t>11,54; 63,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,69</t>
+          <t>1,97; 13,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 14,8</t>
+          <t>3,38; 14,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 17,71</t>
+          <t>5,09; 17,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 16,17</t>
+          <t>3,24; 16,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 15,51</t>
+          <t>2,3; 15,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 8,03</t>
+          <t>-12,31; 8,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,86</t>
+          <t>4,38; 12,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 13,61</t>
+          <t>4,52; 13,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 11,07</t>
+          <t>-2,54; 10,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,25; 117,91</t>
+          <t>11,18; 117,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,06; 124,17</t>
+          <t>20,3; 130,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,6; 150,62</t>
+          <t>28,71; 149,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 67,61</t>
+          <t>11,15; 68,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 63,78</t>
+          <t>7,4; 63,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 30,56</t>
+          <t>-40,98; 31,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,1; 68,96</t>
+          <t>18,73; 69,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,48; 71,06</t>
+          <t>20,32; 70,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 56,91</t>
+          <t>-11,08; 54,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 16,52</t>
+          <t>1,11; 16,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 7,41</t>
+          <t>-5,43; 7,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,71</t>
+          <t>-4,74; 7,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 26,04</t>
+          <t>8,53; 25,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 9,79</t>
+          <t>-6,22; 10,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 9,6</t>
+          <t>-3,64; 9,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,53; 18,72</t>
+          <t>7,36; 17,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 6,46</t>
+          <t>-4,62; 6,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 7,16</t>
+          <t>-1,71; 7,48</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,05; 161,74</t>
+          <t>2,68; 167,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 74,58</t>
+          <t>-32,79; 76,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 75,46</t>
+          <t>-27,62; 74,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28,91; 153,77</t>
+          <t>33,12; 157,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 56,6</t>
+          <t>-25,27; 58,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 55,66</t>
+          <t>-14,36; 58,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,72; 128,72</t>
+          <t>33,86; 119,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 43,81</t>
+          <t>-22,7; 39,65</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 49,54</t>
+          <t>-8,95; 51,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 11,93</t>
+          <t>-1,81; 11,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 13,83</t>
+          <t>-0,3; 13,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,13; 18,32</t>
+          <t>5,09; 18,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 6,29</t>
+          <t>-8,96; 6,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 7,15</t>
+          <t>-8,3; 7,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 13,99</t>
+          <t>-0,56; 14,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,99</t>
+          <t>-3,02; 6,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 8,07</t>
+          <t>-2,34; 7,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,47; 14,18</t>
+          <t>4,66; 13,71</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 89,39</t>
+          <t>-10,6; 85,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,76; 105,31</t>
+          <t>-2,16; 96,37</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23,29; 137,04</t>
+          <t>22,49; 132,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-26,52; 24,19</t>
+          <t>-26,05; 25,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 26,4</t>
+          <t>-23,86; 26,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 51,59</t>
+          <t>-1,98; 52,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 33,26</t>
+          <t>-11,68; 30,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 37,6</t>
+          <t>-9,18; 36,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,19; 67,29</t>
+          <t>15,51; 63,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,24</t>
+          <t>-4,98; 3,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 7,22</t>
+          <t>-1,9; 6,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 9,48</t>
+          <t>0,25; 9,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,14</t>
+          <t>-3,94; 5,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,14</t>
+          <t>-4,61; 5,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 6,5</t>
+          <t>-14,83; 7,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,61</t>
+          <t>-2,98; 3,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,2</t>
+          <t>-1,31; 4,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 6,0</t>
+          <t>-7,54; 5,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 25,14</t>
+          <t>-27,61; 23,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 52,2</t>
+          <t>-10,68; 47,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2,48; 68,69</t>
+          <t>1,38; 67,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 26,79</t>
+          <t>-14,04; 25,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 21,94</t>
+          <t>-17,06; 22,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,27; 27,03</t>
+          <t>-54,79; 29,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 19,25</t>
+          <t>-13,75; 18,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 27,33</t>
+          <t>-5,77; 26,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 30,17</t>
+          <t>-33,63; 28,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,43</t>
+          <t>-4,42; 3,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -1,73</t>
+          <t>-8,92; -1,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 54,15</t>
+          <t>-1,95; 54,38</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,33</t>
+          <t>-7,01; 2,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 0,32</t>
+          <t>-8,74; 0,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 4,53</t>
+          <t>-4,29; 4,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,82</t>
+          <t>-4,16; 1,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -1,88</t>
+          <t>-7,85; -2,14</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 36,14</t>
+          <t>-1,11; 38,42</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 22,02</t>
+          <t>-23,33; 20,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-45,15; -10,12</t>
+          <t>-45,09; -8,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 342,03</t>
+          <t>-11,19; 341,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 9,78</t>
+          <t>-23,63; 10,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 1,05</t>
+          <t>-30,77; 0,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 19,16</t>
+          <t>-14,75; 18,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 8,85</t>
+          <t>-17,61; 7,66</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -8,98</t>
+          <t>-33,4; -10,21</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 159,67</t>
+          <t>-5,23; 181,05</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,92</t>
+          <t>0,19; 3,99</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,72</t>
+          <t>-0,84; 2,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,13; 30,73</t>
+          <t>5,02; 26,48</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,1</t>
+          <t>-0,08; 4,28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,98</t>
+          <t>-3,02; 1,18</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,88</t>
+          <t>-4,18; 3,76</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,45</t>
+          <t>0,63; 3,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,44</t>
+          <t>-1,45; 1,36</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,98</t>
+          <t>2,64; 15,35</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1,82; 26,22</t>
+          <t>1,08; 26,39</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 18,29</t>
+          <t>-5,02; 18,39</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>31,91; 197,18</t>
+          <t>30,71; 169,54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 15,83</t>
+          <t>-0,39; 16,33</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,73</t>
+          <t>-10,76; 4,6</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 14,6</t>
+          <t>-14,66; 14,15</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,52; 16,51</t>
+          <t>2,79; 16,73</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 6,87</t>
+          <t>-6,57; 6,37</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>11,77; 66,1</t>
+          <t>12,12; 71,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,58</t>
+          <t>-2,43; 11,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 10,52</t>
+          <t>-2,73; 10,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,8</t>
+          <t>-2,11; 10,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 19,71</t>
+          <t>1,91; 18,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 18,94</t>
+          <t>3,18; 19,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 16,61</t>
+          <t>2,07; 15,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,57</t>
+          <t>2,14; 12,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,89</t>
+          <t>1,98; 12,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,32</t>
+          <t>2,33; 11,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 88,24</t>
+          <t>-12,55; 86,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 78,97</t>
+          <t>-14,74; 78,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 93,26</t>
+          <t>-10,16; 78,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 99,71</t>
+          <t>4,39; 89,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 96,76</t>
+          <t>11,09; 94,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 85,77</t>
+          <t>7,32; 81,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 70,18</t>
+          <t>9,06; 71,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 71,56</t>
+          <t>8,39; 70,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 68,95</t>
+          <t>9,33; 65,99</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,38</t>
+          <t>-5,44; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 2,16</t>
+          <t>-6,7; 2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 11,71</t>
+          <t>2,26; 12,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 3,38</t>
+          <t>-8,3; 3,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -2,93</t>
+          <t>-14,51; -3,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 5,12</t>
+          <t>-6,25; 4,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,39</t>
+          <t>-5,13; 2,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,54</t>
+          <t>-8,95; -1,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,83</t>
+          <t>-1,08; 6,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,68%</t>
+          <t>-3,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 31,18</t>
+          <t>-30,04; 34,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 16,23</t>
+          <t>-36,28; 17,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 83,69</t>
+          <t>10,32; 89,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 12,12</t>
+          <t>-24,71; 11,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,1; -10,46</t>
+          <t>-43,09; -11,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 17,92</t>
+          <t>-18,07; 16,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 11,12</t>
+          <t>-20,33; 11,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,98; -7,89</t>
+          <t>-35,81; -6,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 32,76</t>
+          <t>-4,42; 29,51</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,03</t>
+          <t>-2,67; 8,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 6,52</t>
+          <t>-4,7; 5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 18,67</t>
+          <t>7,43; 18,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 4,27</t>
+          <t>-9,73; 3,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -2,43</t>
+          <t>-15,86; -2,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 9,25</t>
+          <t>-3,75; 8,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 4,48</t>
+          <t>-4,6; 4,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -0,07</t>
+          <t>-8,57; -0,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,95</t>
+          <t>3,33; 11,56</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 83,18</t>
+          <t>-18,11; 83,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 68,33</t>
+          <t>-29,99; 57,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,31; 181,03</t>
+          <t>45,08; 186,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 17,83</t>
+          <t>-31,82; 14,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,9; -9,03</t>
+          <t>-49,41; -8,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 37,43</t>
+          <t>-12,32; 32,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 24,24</t>
+          <t>-19,7; 25,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 0,48</t>
+          <t>-37,36; -0,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,54; 63,11</t>
+          <t>14,58; 62,48</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,35</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>8,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 13,22</t>
+          <t>2,06; 13,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 14,96</t>
+          <t>3,1; 14,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,98</t>
+          <t>3,91; 17,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,73</t>
+          <t>2,6; 15,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 15,86</t>
+          <t>2,86; 16,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 8,19</t>
+          <t>0,35; 13,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,99</t>
+          <t>4,13; 12,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 13,55</t>
+          <t>4,79; 14,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,85</t>
+          <t>4,41; 13,39</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,35%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,18; 117,49</t>
+          <t>11,59; 119,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,3; 130,64</t>
+          <t>17,93; 131,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,71; 149,12</t>
+          <t>24,13; 151,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,15; 68,33</t>
+          <t>8,94; 65,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 63,81</t>
+          <t>8,38; 67,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 31,81</t>
+          <t>1,15; 54,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,73; 69,24</t>
+          <t>19,2; 69,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,32; 70,73</t>
+          <t>21,13; 73,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 54,23</t>
+          <t>19,57; 70,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 16,77</t>
+          <t>1,39; 16,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 7,91</t>
+          <t>-6,23; 7,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 7,55</t>
+          <t>-5,16; 7,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 25,92</t>
+          <t>7,62; 25,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 10,05</t>
+          <t>-6,68; 9,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 9,97</t>
+          <t>-5,28; 9,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 17,96</t>
+          <t>7,15; 18,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 6,16</t>
+          <t>-4,89; 6,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,48</t>
+          <t>-2,72; 7,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2,68; 167,29</t>
+          <t>8,84; 164,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 76,09</t>
+          <t>-36,17; 68,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 74,39</t>
+          <t>-31,57; 68,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33,12; 157,08</t>
+          <t>28,54; 150,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 58,31</t>
+          <t>-25,85; 58,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 58,44</t>
+          <t>-19,59; 58,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,86; 119,14</t>
+          <t>32,32; 123,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 39,65</t>
+          <t>-22,83; 41,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 51,66</t>
+          <t>-13,87; 49,38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11,93</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,19</t>
+          <t>8,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 11,95</t>
+          <t>-1,16; 12,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 13,32</t>
+          <t>-0,59; 13,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,09; 18,26</t>
+          <t>4,17; 17,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 6,76</t>
+          <t>-9,4; 6,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 7,3</t>
+          <t>-8,53; 7,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 14,72</t>
+          <t>-0,03; 13,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,63</t>
+          <t>-3,36; 6,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,95</t>
+          <t>-1,91; 8,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,71</t>
+          <t>3,81; 13,82</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 85,51</t>
+          <t>-7,48; 90,18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 96,37</t>
+          <t>-2,85; 103,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22,49; 132,47</t>
+          <t>19,75; 128,31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 25,51</t>
+          <t>-27,1; 25,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 26,61</t>
+          <t>-23,63; 30,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 52,76</t>
+          <t>0,05; 51,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 30,36</t>
+          <t>-12,66; 31,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 36,28</t>
+          <t>-7,45; 40,11</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15,51; 63,62</t>
+          <t>13,58; 64,3</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>5,38</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,3</t>
+          <t>-5,26; 3,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,56</t>
+          <t>-1,48; 6,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 9,3</t>
+          <t>0,85; 9,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 5,94</t>
+          <t>-3,45; 6,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 5,23</t>
+          <t>-4,42; 5,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 7,16</t>
+          <t>1,01; 9,86</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,47</t>
+          <t>-2,93; 3,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,94</t>
+          <t>-1,81; 4,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,77</t>
+          <t>2,53; 8,91</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-9,59%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 23,14</t>
+          <t>-28,78; 23,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 47,99</t>
+          <t>-8,63; 50,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,38; 67,71</t>
+          <t>4,84; 69,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 25,8</t>
+          <t>-12,76; 26,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 22,17</t>
+          <t>-15,8; 23,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-54,79; 29,25</t>
+          <t>3,45; 42,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 18,12</t>
+          <t>-12,78; 17,87</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 26,09</t>
+          <t>-8,12; 26,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 28,48</t>
+          <t>11,1; 47,2</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21,21</t>
+          <t>-1,28</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,31</t>
+          <t>-0,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,26</t>
+          <t>-4,53; 3,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -1,6</t>
+          <t>-8,88; -1,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 54,38</t>
+          <t>-5,11; 2,46</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 2,42</t>
+          <t>-6,85; 1,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,22</t>
+          <t>-8,89; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,5</t>
+          <t>-4,79; 3,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,59</t>
+          <t>-4,33; 1,41</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -2,14</t>
+          <t>-7,61; -1,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 38,42</t>
+          <t>-3,46; 1,74</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>120,53%</t>
+          <t>-7,3%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>-2,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>-4,32%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 20,8</t>
+          <t>-23,4; 22,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -8,33</t>
+          <t>-45,43; -10,21</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 341,96</t>
+          <t>-26,17; 16,45</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 10,27</t>
+          <t>-23,86; 8,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 0,9</t>
+          <t>-30,51; 0,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 18,52</t>
+          <t>-16,77; 14,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 7,66</t>
+          <t>-18,51; 6,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -10,21</t>
+          <t>-32,43; -9,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 181,05</t>
+          <t>-14,41; 9,02</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>4,29</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,99</t>
+          <t>0,1; 3,93</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,78</t>
+          <t>-0,95; 2,69</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,02; 26,48</t>
+          <t>3,49; 7,09</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,28</t>
+          <t>-0,31; 4,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,18</t>
+          <t>-3,24; 1,29</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,76</t>
+          <t>1,06; 5,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,53</t>
+          <t>0,59; 3,48</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,36</t>
+          <t>-1,48; 1,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2,64; 15,35</t>
+          <t>2,9; 5,59</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1,08; 26,39</t>
+          <t>0,95; 26,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 18,39</t>
+          <t>-5,64; 17,92</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>30,71; 169,54</t>
+          <t>20,55; 47,54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 16,33</t>
+          <t>-1,08; 15,62</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 4,6</t>
+          <t>-11,51; 4,87</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 14,15</t>
+          <t>3,69; 19,6</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,73</t>
+          <t>2,54; 16,61</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 6,37</t>
+          <t>-6,71; 6,8</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>12,12; 71,05</t>
+          <t>12,94; 26,66</t>
         </is>
       </c>
     </row>
